--- a/data/reference/ucr_courses_enriched.xlsx
+++ b/data/reference/ucr_courses_enriched.xlsx
@@ -847,7 +847,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>This course develops practical financial decision-making skills through case studies and real-world applications. Students learn to analyze financial data, assess risks, and make informed investment, budgeting, and business decisions that enhance value, financial security, and long-term planning.</t>
+          <t>We study financial markets (stocks, bonds, derivatives) and financial institutions (commercial banks and central banks). We address such questions as: Can you outperform the stock market? Why are banks inherently fragile? What do central banks do? What causes financial crises? Throughout the semester, student teams participate in a business simulation, the Stanford Banking Game. Each team manages a virtual bank and tries to maximize its share price.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>See how companies figure out what customers love and what they don’t. You’ll plan and carry out real research, analyze what you find, and share your results. Our course shows you how to gather opinions and turn them into smart business ideas—perfect for future marketers, analysts, or entrepreneurs.</t>
+          <t>See how companies figure out what customers love and what they don’t. You’ll plan and carry out real research, analyze what you find, and share your results. Our course shows you how to gather opinions and turn them into smart business ideas. Ready to turn curiosity into career skills? Perfect for future marketers, analysts, or entrepreneurs.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Leadership &amp; Diversity Management explores how diverse perspectives and experiences shape effective leadership in dynamic, varied environments. Blending cutting-edge theories with hands-on practice, students develop the skills to lead with empathy, inclusivity, and adaptability. Through engaging case studies, interactive workshops, and reflective assessments, participants build awareness of diversity and learn to inspire ethical, collaborative teams.</t>
+          <t>What does it take to lead effectively through pressure, conflict, and diversity? Explore how emotion, identity, belonging, and inclusion shape leadership, teamwork, and performance. Design and conduct an original empirical study while building career-ready skills in research design, data analysis, teamwork, ethical decision-making, and scientific communication.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Leadership &amp; Diversity Management</t>
+          <t>Psychology of Leading Under Pressure</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>History Research Seminar</t>
+          <t>Researching the “American Century”</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Advanced Research Seminar</t>
+          <t>Advanced Research Methods &amp; Statistics</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Explores the archaeology of community and democracy in early-democratic Greece, seeking ancient lessons on community decision-making.</t>
+          <t>The invention of democracy in classical Greece changed the nature of community decision-making, perhaps forever. This process is reflected in the material culture of the period. By examining the archaeology of community &amp; democracy in early-democratic Greece, this course goes in search of ancient lessons for the modern world.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">

--- a/data/reference/ucr_courses_enriched.xlsx
+++ b/data/reference/ucr_courses_enriched.xlsx
@@ -885,6 +885,36 @@
           <t>X</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>BENBUSI312.pdf</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2027h1</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Examines financial markets and institutions, including the pricing of bonds, stocks and derivatives, interest rates and their risk and term structure, commercial-bank balance sheets and performance, financial structure and regulation, banking fragility and financial crises, central banks, money creation and monetary policy. Students apply algebraic and graphical analysis to financial and monetary problems. In the Stanford Banking Game they manage a simulated bank, analyse performance in Excel dashboards, forecast financial statements, and make evidence-based decisions about loans, deposits, capital, liquidity and risk. A small research project extends a selected financial or monetary research article through additional literature, a case study or updated evidence.</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Finance; Monetary economics; Banking</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Financial markets and institutions; Bond, stock and derivative pricing; Interest-rate determination; Interest-rate risk and the term structure; Commercial-bank balance sheets and performance; Bank capital, liquidity and risk management; Financial structure and regulation; Banking fragility; Financial crises in advanced and emerging economies; Central banking; Money supply; Monetary-policy tools and conduct</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Algebraic and graphical financial analysis; Balance-sheet analysis; Duration gap analysis; Bank-management simulation (Stanford Banking Game); Excel-based financial dashboard construction and performance analysis; Financial-statement forecasting; Research-article extension using literature comparison, case study or updated data</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2145,6 +2175,36 @@
       <c r="P22" t="inlineStr">
         <is>
           <t>X</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>BENLEAD211.pdf</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>2027h1</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Examines how emotion regulation, emotional intelligence, emotional expression and suppression, emotional labor, belonging, identity safety and psychological safety shape leadership and social interaction under conflict, exclusion and interpersonal uncertainty. It emphasises inclusive leadership and ethnic, cultural, sexual and gender minority experiences, with digital emotion regulation as a further strand. Students conduct a supervised quantitative survey project: formulating theory-driven hypotheses, selecting established psychological measures, designing and piloting a Qualtrics survey, recruiting participants ethically, collecting original data and preparing a clean dataset. Individual work applies descriptive statistics, reliability analysis, correlations, group comparisons and introductory multiple regression in SPSS or RStudio, and interprets findings and limitations in empirical reports and evidence-based leadership recommendations.</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Leadership studies; Social psychology; Work and organizational psychology; Psychological measurement; Quantitative social research</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Emotion regulation strategies; Emotional intelligence; Emotional expression and suppression; Emotional labor; Inclusive leadership; Belonging and identity safety; Psychological safety; Ethnic, cultural, sexual and gender minority experiences; Digital emotion regulation; Psychological measurement, reliability and validity; Ethical survey research in diverse populations; Interpretation and limitations of quantitative evidence; Evidence-based leadership recommendations</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Theory-driven hypothesis formulation; Quantitative survey research; Established psychological measure selection and evaluation; Qualtrics survey construction and piloting; Ethical participant recruitment and original data collection; Codebook development, reverse coding and scale scoring; Data cleaning and missing-data documentation; Descriptive statistics; Reliability analysis; Correlation analysis; Group comparisons; Introductory multiple regression in SPSS or RStudio; APA-style empirical reporting</t>
         </is>
       </c>
     </row>
